--- a/detections.xlsx
+++ b/detections.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohom\Desktop\Senior Project\codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1310310D-9E24-4B73-9EA0-517CF6860EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C26CFC9E-B37B-4BF3-AE6D-BF59DECA463F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Detections" sheetId="1" r:id="rId1"/>
@@ -898,14 +898,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="14.36328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="8" width="8" customWidth="1"/>
+    <col min="1" max="1" width="23.08984375" customWidth="1"/>
+    <col min="2" max="2" width="22.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -952,10 +948,10 @@
         <v>0</v>
       </c>
       <c r="G2" s="2">
-        <v>2.2000000000000001E-3</v>
+        <v>2.2009999999999998E-3</v>
       </c>
       <c r="H2" s="2">
-        <v>-0.98560000000000003</v>
+        <v>-0.98560099999999995</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
@@ -976,10 +972,10 @@
         <v>0</v>
       </c>
       <c r="G3" s="2">
-        <v>5.8999999999999999E-3</v>
+        <v>5.901E-3</v>
       </c>
       <c r="H3" s="2">
-        <v>-1.0394000000000001</v>
+        <v>-1.039401</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
@@ -1003,7 +999,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="2">
-        <v>-0.99299999999999999</v>
+        <v>-0.99300999999999995</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
@@ -1024,10 +1020,10 @@
         <v>0</v>
       </c>
       <c r="G5" s="2">
-        <v>-0.39229999999999998</v>
+        <v>-0.39230300000000001</v>
       </c>
       <c r="H5" s="2">
-        <v>-0.84099999999999997</v>
+        <v>-0.84101999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
